--- a/RPGProject/Assets/Project/Data/ExcelData/ResouceItemInfo.xlsx
+++ b/RPGProject/Assets/Project/Data/ExcelData/ResouceItemInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suyb1\Documents\GitHub\RPG\RPGProject\Assets\Project\Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AA1D3B-EECC-412E-B06D-544FD15D2931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F17671-C0AF-4FD4-BBB7-0B87A8F58AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="3600" windowWidth="14790" windowHeight="10695" xr2:uid="{3510F260-6A7D-4843-A2DA-E1BA315C89A0}"/>
+    <workbookView xWindow="18420" yWindow="4785" windowWidth="14790" windowHeight="10695" xr2:uid="{3510F260-6A7D-4843-A2DA-E1BA315C89A0}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
@@ -20,152 +20,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum&lt;ItemType&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>고유 키</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>아이템 이름</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템설명</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 타입</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>활</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equipment</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>타입별테이블에서 ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Destory</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>기준가격</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>판매가능여부</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>버리기 가능 여부</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EquipID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ComsumeID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>소비테이블 키</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자원 테이블 키</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반헬멧</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반옷</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반벨트</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반장갑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반어께</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반신발</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>완드</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>투핸드소드</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>쌍검</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>한손검</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1147,456 +1011,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27433482-0B68-4763-85C6-CA814D549BDC}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <v>101</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2">
-        <v>201</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2">
-        <v>301</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2">
-        <v>401</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2">
-        <v>501</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2">
-        <v>601</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2">
-        <v>701</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2">
-        <v>801</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2">
-        <v>901</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1001</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1101</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C4" s="2"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C8" s="2"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C9" s="2"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C10" s="2"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C11" s="2"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C12" s="2"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C13" s="2"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C14" s="2"/>
+      <c r="G14" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
